--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J259-ModeFixationTarifaire-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J259-ModeFixationTarifaire-RASS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -360,7 +360,7 @@
     <t>57</t>
   </si>
   <si>
-    <t>ARS /ARS PCD Dotation forfait ou prix de journée globalisés (CPOM)</t>
+    <t>Dotation globale de soins ARS et hébergement prix de journée PCD – sous CPOM</t>
   </si>
   <si>
     <t>58</t>
